--- a/data/trending_integrated_20260918_09.xlsx
+++ b/data/trending_integrated_20260918_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,60 +563,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1810000</v>
+        <v>20200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+3.72%</t>
+          <t>'+12.66%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.1</v>
+        <v>0.38</v>
       </c>
       <c r="E2" t="n">
-        <v>512</v>
+        <v>43</v>
       </c>
       <c r="F2" t="n">
-        <v>339</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>2507</v>
+        <v>84</v>
       </c>
       <c r="H2" t="n">
-        <v>50.1</v>
+        <v>0.98</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1745000</v>
+        <v>17930</v>
       </c>
       <c r="K2" t="n">
-        <v>1810000</v>
+        <v>18400</v>
       </c>
       <c r="L2" t="n">
-        <v>1815000</v>
+        <v>20200</v>
       </c>
       <c r="M2" t="n">
-        <v>1805000</v>
+        <v>17910</v>
       </c>
       <c r="N2" t="n">
-        <v>50.2</v>
+        <v>0.6</v>
       </c>
       <c r="O2" t="n">
-        <v>176946330500</v>
+        <v>27638946330</v>
       </c>
       <c r="P2" t="n">
-        <v>2987000</v>
+        <v>21100</v>
       </c>
       <c r="Q2" t="n">
-        <v>333000</v>
+        <v>9900</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,29 +626,489 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 증시 호조 및 반도체 관련 긍정 뉴스에 따른 상승 기대감. 기관 및 외인 매매 동향 주시.</t>
+          <t>보호예수 해제 물량에도 불구하고 긍정적인 수급과 목표가 상향 기대감이 나타나고 있습니다.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>['보호예수', '수급', '목표가']</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>950260</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>17250</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>'+6.94%</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="E3" t="n">
+        <v>54</v>
+      </c>
+      <c r="F3" t="n">
+        <v>37</v>
+      </c>
+      <c r="G3" t="n">
+        <v>341</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>16130</v>
+      </c>
+      <c r="K3" t="n">
+        <v>16360</v>
+      </c>
+      <c r="L3" t="n">
+        <v>17570</v>
+      </c>
+      <c r="M3" t="n">
+        <v>16170</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="O3" t="n">
+        <v>113235315485</v>
+      </c>
+      <c r="P3" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>장 초반 급등 출발에 대한 기대감이 있으나, 공매도 관련 언급과 매도 의견이 혼재되어 있습니다.</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>['공매도', '거래량']</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1817000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'+4.13%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>543</v>
+      </c>
+      <c r="F4" t="n">
+        <v>353</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2566</v>
+      </c>
+      <c r="H4" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1745000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1810000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1822000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1805000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>516136038000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>333000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>미국 증시 및 반도체 관련 긍정적 뉴스와 실적 전망이 제시되며, 목표 주가 상향 언급이 있습니다.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
         <v>0.6</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>['반도체', 'AI', '실적 전망']</t>
-        </is>
-      </c>
-      <c r="X2" t="n">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['반도체', '실적 전망', 'AI']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
         <v>74</v>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>259000</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'+2.57%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E5" t="n">
+        <v>591</v>
+      </c>
+      <c r="F5" t="n">
+        <v>382</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2778</v>
+      </c>
+      <c r="H5" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>252500</v>
+      </c>
+      <c r="K5" t="n">
+        <v>261000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>261000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>258000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="O5" t="n">
+        <v>374580397000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>78600</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>정치적 이슈와 관련된 언급이 다수이며, 주가 관련 팩트 기반 분석은 부족합니다.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>109</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>86000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'+0.70%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E6" t="n">
+        <v>78</v>
+      </c>
+      <c r="F6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G6" t="n">
+        <v>626</v>
+      </c>
+      <c r="H6" t="n">
+        <v>23.23</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>85400</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87300</v>
+      </c>
+      <c r="L6" t="n">
+        <v>87800</v>
+      </c>
+      <c r="M6" t="n">
+        <v>85800</v>
+      </c>
+      <c r="N6" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="O6" t="n">
+        <v>26291539900</v>
+      </c>
+      <c r="P6" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>원전 관련 뉴스와 대미 투자 발표 가능성에 대한 언급이 있으며, 긍정적인 전망이 제시됩니다.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['원전', '대미 투자']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>미투온</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4360</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-5.93%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>63</v>
+      </c>
+      <c r="F7" t="n">
+        <v>46</v>
+      </c>
+      <c r="G7" t="n">
+        <v>361</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>4635</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4465</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4535</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4335</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O7" t="n">
+        <v>9617512582</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6900</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1738</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>STO 사업 및 미국 코인 거래 허용 관련 호재 가능성이 언급되나, 주가 하락에 대한 우려도 존재합니다.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['STO', '코인', '호재']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>201490</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260918_09.xlsx
+++ b/data/trending_integrated_20260918_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20200</v>
+        <v>19670</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+12.66%</t>
+          <t>'+9.70%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.38</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="H2" t="n">
         <v>0.98</v>
@@ -601,7 +601,7 @@
         <v>18400</v>
       </c>
       <c r="L2" t="n">
-        <v>20200</v>
+        <v>20400</v>
       </c>
       <c r="M2" t="n">
         <v>17910</v>
@@ -610,7 +610,7 @@
         <v>0.6</v>
       </c>
       <c r="O2" t="n">
-        <v>27638946330</v>
+        <v>41412664545</v>
       </c>
       <c r="P2" t="n">
         <v>21100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>보호예수 해제 물량에도 불구하고 긍정적인 수급과 목표가 상향 기대감이 나타나고 있습니다.</t>
+          <t>빅파마 기술 이전 및 3상 임상 관련 언급과 보호예수 해제 관련 내용이 혼재하며, 투자자들 간의 의견이 상반됨. 긍정적인 수급에 대한 기대와 함께 주의 섞인 언급이 나타남.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['보호예수', '수급', '목표가']</t>
+          <t>['기술이전', '보호예수', '임상']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17250</v>
+        <v>17370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.94%</t>
+          <t>'+7.69%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>341</v>
+        <v>436</v>
       </c>
       <c r="H3" t="n">
         <v>4.61</v>
@@ -693,7 +693,7 @@
         <v>16360</v>
       </c>
       <c r="L3" t="n">
-        <v>17570</v>
+        <v>17920</v>
       </c>
       <c r="M3" t="n">
         <v>16170</v>
@@ -702,7 +702,7 @@
         <v>4.88</v>
       </c>
       <c r="O3" t="n">
-        <v>113235315485</v>
+        <v>198804830335</v>
       </c>
       <c r="P3" t="n">
         <v>31500</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>장 초반 급등 출발에 대한 기대감이 있으나, 공매도 관련 언급과 매도 의견이 혼재되어 있습니다.</t>
+          <t>광통신 관련 해외 종목 상승세와 국내 시장 상황에 대한 언급이 있으나, 공매도 관련 부정적 언급과 투자 주의 메시지가 혼재함. 거래량 증가에 대한 기대가 일부 존재함.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['공매도', '거래량']</t>
+          <t>['광통신', '공매도', '거래량']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1817000</v>
+        <v>1822000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.13%</t>
+          <t>'+4.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>543</v>
+        <v>582</v>
       </c>
       <c r="F4" t="n">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="G4" t="n">
-        <v>2566</v>
+        <v>2683</v>
       </c>
       <c r="H4" t="n">
         <v>50.1</v>
@@ -785,7 +785,7 @@
         <v>1810000</v>
       </c>
       <c r="L4" t="n">
-        <v>1822000</v>
+        <v>1825000</v>
       </c>
       <c r="M4" t="n">
         <v>1805000</v>
@@ -794,7 +794,7 @@
         <v>50.2</v>
       </c>
       <c r="O4" t="n">
-        <v>516136038000</v>
+        <v>705428886500</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>259000</v>
+        <v>260000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.57%</t>
+          <t>'+2.97%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>591</v>
+        <v>654</v>
       </c>
       <c r="F5" t="n">
-        <v>382</v>
+        <v>413</v>
       </c>
       <c r="G5" t="n">
-        <v>2778</v>
+        <v>2894</v>
       </c>
       <c r="H5" t="n">
         <v>46.48</v>
@@ -886,7 +886,7 @@
         <v>46.52</v>
       </c>
       <c r="O5" t="n">
-        <v>374580397000</v>
+        <v>460364014000</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>86000</v>
+        <v>85600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="F6" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="H6" t="n">
         <v>23.23</v>
@@ -972,13 +972,13 @@
         <v>87800</v>
       </c>
       <c r="M6" t="n">
-        <v>85800</v>
+        <v>85600</v>
       </c>
       <c r="N6" t="n">
         <v>23.27</v>
       </c>
       <c r="O6" t="n">
-        <v>26291539900</v>
+        <v>36323676050</v>
       </c>
       <c r="P6" t="n">
         <v>139200</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>원전 관련 뉴스와 대미 투자 발표 가능성에 대한 언급이 있으며, 긍정적인 전망이 제시됩니다.</t>
+          <t>미국 원전주 급등 소식과 대미 투자 발표 가능성이 언급되며 긍정적인 전망이 제시됨. 다만, 구체적인 공시나 확정된 사실보다는 기대감에 기반한 내용이 다수 포함됨.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '대미 투자']</t>
+          <t>['원전주', '대미투자', '발표']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4360</v>
+        <v>4320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-5.93%</t>
+          <t>'-6.80%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
-        <v>361</v>
+        <v>405</v>
       </c>
       <c r="H7" t="n">
         <v>0.55</v>
@@ -1064,13 +1064,13 @@
         <v>4535</v>
       </c>
       <c r="M7" t="n">
-        <v>4335</v>
+        <v>4265</v>
       </c>
       <c r="N7" t="n">
         <v>0.95</v>
       </c>
       <c r="O7" t="n">
-        <v>9617512582</v>
+        <v>14234314709</v>
       </c>
       <c r="P7" t="n">
         <v>6900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>STO 사업 및 미국 코인 거래 허용 관련 호재 가능성이 언급되나, 주가 하락에 대한 우려도 존재합니다.</t>
+          <t>미국 코인형 주식 거래 허용 소식이 STO 사업 추진 중인 계열사와 연계되어 호재로 작용할 가능성이 언급됨. 스테이블 코인 테마 관련주로 분류되며 긍정적인 기대감이 높음.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['STO', '코인', '호재']</t>
+          <t>['STO', '스테이블코인', '코인형주식거래']</t>
         </is>
       </c>
       <c r="X7" t="n">

--- a/data/trending_integrated_20260918_09.xlsx
+++ b/data/trending_integrated_20260918_09.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19670</v>
+        <v>17370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+9.70%</t>
+          <t>'+7.69%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.38</v>
+        <v>-0.27</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="G2" t="n">
-        <v>118</v>
+        <v>516</v>
       </c>
       <c r="H2" t="n">
-        <v>0.98</v>
+        <v>4.61</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,38 +595,38 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>17930</v>
+        <v>16130</v>
       </c>
       <c r="K2" t="n">
-        <v>18400</v>
+        <v>16360</v>
       </c>
       <c r="L2" t="n">
-        <v>20400</v>
+        <v>17920</v>
       </c>
       <c r="M2" t="n">
-        <v>17910</v>
+        <v>16170</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6</v>
+        <v>4.88</v>
       </c>
       <c r="O2" t="n">
-        <v>41412664545</v>
+        <v>232330915245</v>
       </c>
       <c r="P2" t="n">
-        <v>21100</v>
+        <v>31500</v>
       </c>
       <c r="Q2" t="n">
-        <v>9900</v>
+        <v>1272</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>303000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>빅파마 기술 이전 및 3상 임상 관련 언급과 보호예수 해제 관련 내용이 혼재하며, 투자자들 간의 의견이 상반됨. 긍정적인 수급에 대한 기대와 함께 주의 섞인 언급이 나타남.</t>
+          <t>광통신 관련 종목들의 미국 증시 상승 소식이 전해졌으며, 외국인 매수세가 유입되는 것으로 파악됨. 3만원 목표 및 거래량 5천 돌파 독려.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,11 +635,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['기술이전', '보호예수', '임상']</t>
+          <t>['광통신', '외국인 매수', '거래량']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17370</v>
+        <v>19160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.69%</t>
+          <t>'+6.86%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.27</v>
+        <v>0.38</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>436</v>
+        <v>118</v>
       </c>
       <c r="H3" t="n">
-        <v>4.61</v>
+        <v>0.98</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16130</v>
+        <v>17930</v>
       </c>
       <c r="K3" t="n">
-        <v>16360</v>
+        <v>18400</v>
       </c>
       <c r="L3" t="n">
-        <v>17920</v>
+        <v>20400</v>
       </c>
       <c r="M3" t="n">
-        <v>16170</v>
+        <v>17910</v>
       </c>
       <c r="N3" t="n">
-        <v>4.88</v>
+        <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>198804830335</v>
+        <v>48209144135</v>
       </c>
       <c r="P3" t="n">
-        <v>31500</v>
+        <v>21100</v>
       </c>
       <c r="Q3" t="n">
-        <v>1272</v>
+        <v>9900</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>광통신 관련 해외 종목 상승세와 국내 시장 상황에 대한 언급이 있으나, 공매도 관련 부정적 언급과 투자 주의 메시지가 혼재함. 거래량 증가에 대한 기대가 일부 존재함.</t>
+          <t>빅파마 기술이전 가능성과 보호예수 물량 해제 이슈 속에서 수급 개선에 대한 긍정적 분석이 일부 존재함. 목표가 5만원 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광통신', '공매도', '거래량']</t>
+          <t>['기술이전', '보호예수', '수급']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1822000</v>
+        <v>1826000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.41%</t>
+          <t>'+4.64%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>582</v>
+        <v>614</v>
       </c>
       <c r="F4" t="n">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="G4" t="n">
-        <v>2683</v>
+        <v>2813</v>
       </c>
       <c r="H4" t="n">
         <v>50.1</v>
@@ -785,7 +785,7 @@
         <v>1810000</v>
       </c>
       <c r="L4" t="n">
-        <v>1825000</v>
+        <v>1828000</v>
       </c>
       <c r="M4" t="n">
         <v>1805000</v>
@@ -794,7 +794,7 @@
         <v>50.2</v>
       </c>
       <c r="O4" t="n">
-        <v>705428886500</v>
+        <v>882855015500</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -803,7 +803,7 @@
         <v>333000</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>59000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>260000</v>
+        <v>259750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.97%</t>
+          <t>'+2.87%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>654</v>
+        <v>706</v>
       </c>
       <c r="F5" t="n">
-        <v>413</v>
+        <v>443</v>
       </c>
       <c r="G5" t="n">
-        <v>2894</v>
+        <v>2980</v>
       </c>
       <c r="H5" t="n">
         <v>46.48</v>
@@ -886,7 +886,7 @@
         <v>46.52</v>
       </c>
       <c r="O5" t="n">
-        <v>460364014000</v>
+        <v>542475875500</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -895,7 +895,7 @@
         <v>78600</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-413000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>85600</v>
+        <v>85800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="F6" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>650</v>
+        <v>699</v>
       </c>
       <c r="H6" t="n">
         <v>23.23</v>
@@ -972,13 +972,13 @@
         <v>87800</v>
       </c>
       <c r="M6" t="n">
-        <v>85600</v>
+        <v>85300</v>
       </c>
       <c r="N6" t="n">
         <v>23.27</v>
       </c>
       <c r="O6" t="n">
-        <v>36323676050</v>
+        <v>45277592150</v>
       </c>
       <c r="P6" t="n">
         <v>139200</v>
@@ -987,14 +987,14 @@
         <v>57000</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-54000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 소식과 대미 투자 발표 가능성이 언급되며 긍정적인 전망이 제시됨. 다만, 구체적인 공시나 확정된 사실보다는 기대감에 기반한 내용이 다수 포함됨.</t>
+          <t>미국 원전주 급등과 대미 투자 관련 발표 가능성 뉴스를 기반으로 주가 상승 기대감이 형성됨. 120일선 돌파 및 장기적 50만원 목표 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전주', '대미투자', '발표']</t>
+          <t>['원전주', '대미 투자', '120일선']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4320</v>
+        <v>4295</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-6.80%</t>
+          <t>'-7.34%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G7" t="n">
-        <v>405</v>
+        <v>455</v>
       </c>
       <c r="H7" t="n">
         <v>0.55</v>
@@ -1070,7 +1070,7 @@
         <v>0.95</v>
       </c>
       <c r="O7" t="n">
-        <v>14234314709</v>
+        <v>16124940276</v>
       </c>
       <c r="P7" t="n">
         <v>6900</v>
@@ -1079,23 +1079,23 @@
         <v>1738</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>86000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 코인형 주식 거래 허용 소식이 STO 사업 추진 중인 계열사와 연계되어 호재로 작용할 가능성이 언급됨. 스테이블 코인 테마 관련주로 분류되며 긍정적인 기대감이 높음.</t>
+          <t>미국 스테이블코인 관련 규제 완화 뉴스를 호재로 인식하며 STO 사업 추진과 연계한 기대감이 있으나, 경고 예고 및 급락 가능성 언급으로 부정적 전망도 혼재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['STO', '스테이블코인', '코인형주식거래']</t>
+          <t>['STO', '스테이블코인', '호재']</t>
         </is>
       </c>
       <c r="X7" t="n">

--- a/data/trending_integrated_20260918_09.xlsx
+++ b/data/trending_integrated_20260918_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17370</v>
+        <v>8700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+7.69%</t>
+          <t>'+23.93%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.27</v>
+        <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>516</v>
+        <v>88</v>
       </c>
       <c r="H2" t="n">
-        <v>4.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>16130</v>
+        <v>7020</v>
       </c>
       <c r="K2" t="n">
-        <v>16360</v>
+        <v>7180</v>
       </c>
       <c r="L2" t="n">
-        <v>17920</v>
+        <v>8890</v>
       </c>
       <c r="M2" t="n">
-        <v>16170</v>
+        <v>7150</v>
       </c>
       <c r="N2" t="n">
-        <v>4.88</v>
+        <v>0.59</v>
       </c>
       <c r="O2" t="n">
-        <v>232330915245</v>
+        <v>97143598660</v>
       </c>
       <c r="P2" t="n">
-        <v>31500</v>
+        <v>16200</v>
       </c>
       <c r="Q2" t="n">
-        <v>1272</v>
+        <v>1206</v>
       </c>
       <c r="R2" t="n">
-        <v>303000</v>
+        <v>220000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>광통신 관련 종목들의 미국 증시 상승 소식이 전해졌으며, 외국인 매수세가 유입되는 것으로 파악됨. 3만원 목표 및 거래량 5천 돌파 독려.</t>
+          <t>금일 상한가 안착 시 10,000원 돌파 기대감. 8,000원 안착 후 상승 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '외국인 매수', '거래량']</t>
+          <t>['상한가', '돌파']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19160</v>
+        <v>13610</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.86%</t>
+          <t>'+17.53%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.38</v>
+        <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="H3" t="n">
-        <v>0.98</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>17930</v>
+        <v>11580</v>
       </c>
       <c r="K3" t="n">
-        <v>18400</v>
+        <v>12200</v>
       </c>
       <c r="L3" t="n">
-        <v>20400</v>
+        <v>13820</v>
       </c>
       <c r="M3" t="n">
-        <v>17910</v>
+        <v>12100</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>48209144135</v>
+        <v>79857412920</v>
       </c>
       <c r="P3" t="n">
-        <v>21100</v>
+        <v>21150</v>
       </c>
       <c r="Q3" t="n">
-        <v>9900</v>
+        <v>8140</v>
       </c>
       <c r="R3" t="n">
-        <v>50000</v>
+        <v>278000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>빅파마 기술이전 가능성과 보호예수 물량 해제 이슈 속에서 수급 개선에 대한 긍정적 분석이 일부 존재함. 목표가 5만원 제시.</t>
+          <t>모더나 관련 언급과 함께 단기적인 주가 반등 기대감이 있으나, 구체적인 근거 제시 부족.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['기술이전', '보호예수', '수급']</t>
+          <t>['모더나', '호재']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,67 +740,67 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1826000</v>
+        <v>6720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.64%</t>
+          <t>'+14.29%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.1</v>
+        <v>1.02</v>
       </c>
       <c r="E4" t="n">
-        <v>614</v>
+        <v>46</v>
       </c>
       <c r="F4" t="n">
-        <v>391</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>2813</v>
+        <v>31</v>
       </c>
       <c r="H4" t="n">
-        <v>50.1</v>
+        <v>2.85</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1745000</v>
+        <v>5880</v>
       </c>
       <c r="K4" t="n">
-        <v>1810000</v>
+        <v>5950</v>
       </c>
       <c r="L4" t="n">
-        <v>1828000</v>
+        <v>6920</v>
       </c>
       <c r="M4" t="n">
-        <v>1805000</v>
+        <v>5840</v>
       </c>
       <c r="N4" t="n">
-        <v>50.2</v>
+        <v>1.83</v>
       </c>
       <c r="O4" t="n">
-        <v>882855015500</v>
+        <v>42124529275</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>11760</v>
       </c>
       <c r="Q4" t="n">
-        <v>333000</v>
+        <v>1620</v>
       </c>
       <c r="R4" t="n">
         <v>59000</v>
@@ -810,20 +810,20 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 증시 및 반도체 관련 긍정적 뉴스와 실적 전망이 제시되며, 목표 주가 상향 언급이 있습니다.</t>
+          <t>변압기 관련 테마 언급과 함께 3연상 목표 기대감. 프로그램 매수세 지속.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '실적 전망', 'AI']</t>
+          <t>['변압기', '프로그램매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>259750</v>
+        <v>17850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.87%</t>
+          <t>'+10.66%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.04</v>
+        <v>-0.27</v>
       </c>
       <c r="E5" t="n">
-        <v>706</v>
+        <v>99</v>
       </c>
       <c r="F5" t="n">
-        <v>443</v>
+        <v>72</v>
       </c>
       <c r="G5" t="n">
-        <v>2980</v>
+        <v>628</v>
       </c>
       <c r="H5" t="n">
-        <v>46.48</v>
+        <v>4.61</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>252500</v>
+        <v>16130</v>
       </c>
       <c r="K5" t="n">
-        <v>261000</v>
+        <v>16360</v>
       </c>
       <c r="L5" t="n">
-        <v>261000</v>
+        <v>18000</v>
       </c>
       <c r="M5" t="n">
-        <v>258000</v>
+        <v>16170</v>
       </c>
       <c r="N5" t="n">
-        <v>46.52</v>
+        <v>4.88</v>
       </c>
       <c r="O5" t="n">
-        <v>542475875500</v>
+        <v>297306907260</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>78600</v>
+        <v>1272</v>
       </c>
       <c r="R5" t="n">
-        <v>-413000</v>
+        <v>303000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 언급이 다수이며, 주가 관련 팩트 기반 분석은 부족합니다.</t>
+          <t>미국 증시 강세와 외국인 매수세 유입 언급. 거래량 증가 및 3만원 목표 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['외국인매수', '거래량']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>85800</v>
+        <v>19260</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.47%</t>
+          <t>'+7.42%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.04</v>
+        <v>0.38</v>
       </c>
       <c r="E6" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>699</v>
+        <v>131</v>
       </c>
       <c r="H6" t="n">
-        <v>23.23</v>
+        <v>0.98</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>85400</v>
+        <v>17930</v>
       </c>
       <c r="K6" t="n">
-        <v>87300</v>
+        <v>18400</v>
       </c>
       <c r="L6" t="n">
-        <v>87800</v>
+        <v>20400</v>
       </c>
       <c r="M6" t="n">
-        <v>85300</v>
+        <v>17910</v>
       </c>
       <c r="N6" t="n">
-        <v>23.27</v>
+        <v>0.6</v>
       </c>
       <c r="O6" t="n">
-        <v>45277592150</v>
+        <v>51662256795</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>21100</v>
       </c>
       <c r="Q6" t="n">
-        <v>57000</v>
+        <v>9900</v>
       </c>
       <c r="R6" t="n">
-        <v>-54000</v>
+        <v>50000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 원전주 급등과 대미 투자 관련 발표 가능성 뉴스를 기반으로 주가 상승 기대감이 형성됨. 120일선 돌파 및 장기적 50만원 목표 제시.</t>
+          <t>빅파마 기술이전 및 3상 임상 관련 기대감. 보호예수 물량 해제 이슈 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전주', '대미 투자', '120일선']</t>
+          <t>['기술이전', '보호예수']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,97 +1016,557 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4295</v>
+        <v>19540</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-7.34%</t>
+          <t>'+5.68%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.4</v>
+        <v>-0.11</v>
       </c>
       <c r="E7" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>455</v>
+        <v>159</v>
       </c>
       <c r="H7" t="n">
-        <v>0.55</v>
+        <v>10.74</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>4635</v>
+        <v>18490</v>
       </c>
       <c r="K7" t="n">
-        <v>4465</v>
+        <v>18900</v>
       </c>
       <c r="L7" t="n">
-        <v>4535</v>
+        <v>19550</v>
       </c>
       <c r="M7" t="n">
-        <v>4265</v>
+        <v>18770</v>
       </c>
       <c r="N7" t="n">
-        <v>0.95</v>
+        <v>10.85</v>
       </c>
       <c r="O7" t="n">
-        <v>16124940276</v>
+        <v>44287793470</v>
       </c>
       <c r="P7" t="n">
-        <v>6900</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>1738</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>86000</v>
+        <v>42000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 스테이블코인 관련 규제 완화 뉴스를 호재로 인식하며 STO 사업 추진과 연계한 기대감이 있으나, 경고 예고 및 급락 가능성 언급으로 부정적 전망도 혼재.</t>
+          <t>미국 원전주 상승세 및 중동 전쟁 종전 논의 언급. 대차해지 운동을 통한 주가 부양 시도.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['원전주', '대차해지']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'+4.30%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>656</v>
+      </c>
+      <c r="F8" t="n">
+        <v>413</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2928</v>
+      </c>
+      <c r="H8" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1745000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1810000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1828000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1805000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1014303763000</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>333000</v>
+      </c>
+      <c r="R8" t="n">
+        <v>59000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>미국 증시 및 반도체 관련 긍정적 뉴스와 실적 전망이 제시되며, 목표 주가 상향 언급이 있습니다.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['반도체', '실적 전망', 'AI']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>74</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>엑스게이트</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>17770</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'+3.01%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E9" t="n">
+        <v>42</v>
+      </c>
+      <c r="F9" t="n">
+        <v>32</v>
+      </c>
+      <c r="G9" t="n">
+        <v>67</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>17250</v>
+      </c>
+      <c r="K9" t="n">
+        <v>17920</v>
+      </c>
+      <c r="L9" t="n">
+        <v>18440</v>
+      </c>
+      <c r="M9" t="n">
+        <v>17450</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>55556356035</v>
+      </c>
+      <c r="P9" t="n">
+        <v>30550</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6100</v>
+      </c>
+      <c r="R9" t="n">
+        <v>21000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>미국 양자컴퓨터주 급등에 따른 국내 양자컴퓨터 테마 기대감. AI 반도체, 보안 테마 연관성 언급.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['양자컴퓨터', 'AI반도체']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>356680</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>259500</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'+2.77%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E10" t="n">
+        <v>748</v>
+      </c>
+      <c r="F10" t="n">
+        <v>464</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3060</v>
+      </c>
+      <c r="H10" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>252500</v>
+      </c>
+      <c r="K10" t="n">
+        <v>261000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>261000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>258000</v>
+      </c>
+      <c r="N10" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="O10" t="n">
+        <v>605444648000</v>
+      </c>
+      <c r="P10" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>78600</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-413000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>정치적 이슈와 관련된 언급이 다수이며, 주가 관련 팩트 기반 분석은 부족합니다.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
         <v>0.1</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>['STO', '스테이블코인', '호재']</t>
-        </is>
-      </c>
-      <c r="X7" t="n">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>109</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>85850</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'+0.53%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E11" t="n">
+        <v>122</v>
+      </c>
+      <c r="F11" t="n">
+        <v>78</v>
+      </c>
+      <c r="G11" t="n">
+        <v>717</v>
+      </c>
+      <c r="H11" t="n">
+        <v>23.23</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>85400</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87300</v>
+      </c>
+      <c r="L11" t="n">
+        <v>87800</v>
+      </c>
+      <c r="M11" t="n">
+        <v>85300</v>
+      </c>
+      <c r="N11" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="O11" t="n">
+        <v>49877104000</v>
+      </c>
+      <c r="P11" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-54000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>미국 원전주 급등과 대미 투자 관련 발표 가능성 뉴스를 기반으로 주가 상승 기대감이 형성됨. 120일선 돌파 및 장기적 50만원 목표 제시.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['원전주', '대미 투자', '120일선']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>미투온</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4280</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-7.66%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>97</v>
+      </c>
+      <c r="F12" t="n">
+        <v>67</v>
+      </c>
+      <c r="G12" t="n">
+        <v>494</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>4635</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4465</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4535</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4225</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O12" t="n">
+        <v>18645199636</v>
+      </c>
+      <c r="P12" t="n">
+        <v>6900</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1738</v>
+      </c>
+      <c r="R12" t="n">
+        <v>86000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>STO 사업 추진 및 미국 코인 주식 거래 허용 호재 언급. 스테이블코인 테마 관련 기대감.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['STO', '스테이블코인']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>3</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>201490</t>
         </is>

--- a/data/trending_integrated_20260918_09.xlsx
+++ b/data/trending_integrated_20260918_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8700</v>
+        <v>8550</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.93%</t>
+          <t>'+21.79%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.59</v>
       </c>
       <c r="O2" t="n">
-        <v>97143598660</v>
+        <v>106437157060</v>
       </c>
       <c r="P2" t="n">
         <v>16200</v>
@@ -619,14 +619,14 @@
         <v>1206</v>
       </c>
       <c r="R2" t="n">
-        <v>220000</v>
+        <v>574000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>금일 상한가 안착 시 10,000원 돌파 기대감. 8,000원 안착 후 상승 전망.</t>
+          <t>상한가 안착 시 10000원 돌파 기대. 8000원대 안착 목표. 26% 수익률 및 8천만원 수익 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['상한가', '돌파']</t>
+          <t>['상한가', '수익률', '매물대']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13610</v>
+        <v>13460</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.53%</t>
+          <t>'+16.23%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="H3" t="n">
         <v>8.029999999999999</v>
@@ -702,7 +702,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>79857412920</v>
+        <v>86874784840</v>
       </c>
       <c r="P3" t="n">
         <v>21150</v>
@@ -711,14 +711,14 @@
         <v>8140</v>
       </c>
       <c r="R3" t="n">
-        <v>278000</v>
+        <v>540000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>모더나 관련 언급과 함께 단기적인 주가 반등 기대감이 있으나, 구체적인 근거 제시 부족.</t>
+          <t>뉴스 기대감, 프로그램 매수 증가 언급. 2030년까지 운이 트일 것이라는 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['모더나', '호재']</t>
+          <t>['셀그램', '모더나', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6720</v>
+        <v>6740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.29%</t>
+          <t>'+14.63%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1.02</v>
       </c>
       <c r="E4" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H4" t="n">
         <v>2.85</v>
@@ -794,7 +794,7 @@
         <v>1.83</v>
       </c>
       <c r="O4" t="n">
-        <v>42124529275</v>
+        <v>53182036955</v>
       </c>
       <c r="P4" t="n">
         <v>11760</v>
@@ -803,23 +803,23 @@
         <v>1620</v>
       </c>
       <c r="R4" t="n">
-        <v>59000</v>
+        <v>900000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>변압기 관련 테마 언급과 함께 3연상 목표 기대감. 프로그램 매수세 지속.</t>
+          <t>변압기 관련 기대감. 개미만 털린다는 부정적 전망과 함께 종가상 기대 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['변압기', '프로그램매수']</t>
+          <t>['변압기', '개미', '종가상']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17850</v>
+        <v>24550</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.66%</t>
+          <t>'+13.66%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.27</v>
+        <v>-0.2</v>
       </c>
       <c r="E5" t="n">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="F5" t="n">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>628</v>
+        <v>91</v>
       </c>
       <c r="H5" t="n">
-        <v>4.61</v>
+        <v>2.41</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16130</v>
+        <v>21600</v>
       </c>
       <c r="K5" t="n">
-        <v>16360</v>
+        <v>22250</v>
       </c>
       <c r="L5" t="n">
-        <v>18000</v>
+        <v>25150</v>
       </c>
       <c r="M5" t="n">
-        <v>16170</v>
+        <v>21700</v>
       </c>
       <c r="N5" t="n">
-        <v>4.88</v>
+        <v>2.61</v>
       </c>
       <c r="O5" t="n">
-        <v>297306907260</v>
+        <v>141098407475</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>59600</v>
       </c>
       <c r="Q5" t="n">
-        <v>1272</v>
+        <v>1030</v>
       </c>
       <c r="R5" t="n">
-        <v>303000</v>
+        <v>-241000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 증시 강세와 외국인 매수세 유입 언급. 거래량 증가 및 3만원 목표 기대감.</t>
+          <t>박스권 상단 돌파 후 25000원 목표 설정. 통신주 하락 속에서 재시도 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외국인매수', '거래량']</t>
+          <t>['박스권', '통신주', '목표가']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19260</v>
+        <v>18110</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.42%</t>
+          <t>'+12.28%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.38</v>
+        <v>-0.27</v>
       </c>
       <c r="E6" t="n">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="G6" t="n">
-        <v>131</v>
+        <v>727</v>
       </c>
       <c r="H6" t="n">
-        <v>0.98</v>
+        <v>4.61</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17930</v>
+        <v>16130</v>
       </c>
       <c r="K6" t="n">
-        <v>18400</v>
+        <v>16360</v>
       </c>
       <c r="L6" t="n">
-        <v>20400</v>
+        <v>18230</v>
       </c>
       <c r="M6" t="n">
-        <v>17910</v>
+        <v>16170</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6</v>
+        <v>4.88</v>
       </c>
       <c r="O6" t="n">
-        <v>51662256795</v>
+        <v>348654002415</v>
       </c>
       <c r="P6" t="n">
-        <v>21100</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>9900</v>
+        <v>1272</v>
       </c>
       <c r="R6" t="n">
-        <v>50000</v>
+        <v>474000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>빅파마 기술이전 및 3상 임상 관련 기대감. 보호예수 물량 해제 이슈 언급.</t>
+          <t>미국 증시 동반 상승, 18000원 돌파 기대. 공매도 비판 및 거래량 증가 독려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['기술이전', '보호예수']</t>
+          <t>['공매도', '거래량', '미국 증시']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19540</v>
+        <v>19070</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.68%</t>
+          <t>'+6.36%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.11</v>
+        <v>0.38</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="H7" t="n">
-        <v>10.74</v>
+        <v>0.98</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18490</v>
+        <v>17930</v>
       </c>
       <c r="K7" t="n">
-        <v>18900</v>
+        <v>18400</v>
       </c>
       <c r="L7" t="n">
-        <v>19550</v>
+        <v>20400</v>
       </c>
       <c r="M7" t="n">
-        <v>18770</v>
+        <v>17910</v>
       </c>
       <c r="N7" t="n">
-        <v>10.85</v>
+        <v>0.6</v>
       </c>
       <c r="O7" t="n">
-        <v>44287793470</v>
+        <v>54086078755</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>21100</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>9900</v>
       </c>
       <c r="R7" t="n">
-        <v>42000</v>
+        <v>24000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 원전주 상승세 및 중동 전쟁 종전 논의 언급. 대차해지 운동을 통한 주가 부양 시도.</t>
+          <t>보호예수 물량 넘기려는 움직임 경계. 빅파마 기술 이전 및 3상 4건 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전주', '대차해지']</t>
+          <t>['보호예수', '기술이전', '3상']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1820000</v>
+        <v>19480</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.30%</t>
+          <t>'+5.35%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="E8" t="n">
-        <v>656</v>
+        <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>413</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>2928</v>
+        <v>171</v>
       </c>
       <c r="H8" t="n">
-        <v>50.1</v>
+        <v>10.74</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1745000</v>
+        <v>18490</v>
       </c>
       <c r="K8" t="n">
-        <v>1810000</v>
+        <v>18900</v>
       </c>
       <c r="L8" t="n">
-        <v>1828000</v>
+        <v>19570</v>
       </c>
       <c r="M8" t="n">
-        <v>1805000</v>
+        <v>18770</v>
       </c>
       <c r="N8" t="n">
-        <v>50.2</v>
+        <v>10.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1014303763000</v>
+        <v>54437734960</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>333000</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>59000</v>
+        <v>213000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 증시 및 반도체 관련 긍정적 뉴스와 실적 전망이 제시되며, 목표 주가 상향 언급이 있습니다.</t>
+          <t>원전주 미국장 상승세 언급. 대차해지 운동 동참 독려. 하반기 상승 및 2만원대 안착 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', '실적 전망', 'AI']</t>
+          <t>['원전주', '대차해지', '하반기 상승']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17770</v>
+        <v>1822000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.01%</t>
+          <t>'+4.41%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.27</v>
+        <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>677</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>421</v>
       </c>
       <c r="G9" t="n">
-        <v>67</v>
+        <v>2983</v>
       </c>
       <c r="H9" t="n">
-        <v>0.97</v>
+        <v>50.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17250</v>
+        <v>1745000</v>
       </c>
       <c r="K9" t="n">
-        <v>17920</v>
+        <v>1810000</v>
       </c>
       <c r="L9" t="n">
-        <v>18440</v>
+        <v>1828000</v>
       </c>
       <c r="M9" t="n">
-        <v>17450</v>
+        <v>1805000</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7</v>
+        <v>50.2</v>
       </c>
       <c r="O9" t="n">
-        <v>55556356035</v>
+        <v>1177310164000</v>
       </c>
       <c r="P9" t="n">
-        <v>30550</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>6100</v>
+        <v>333000</v>
       </c>
       <c r="R9" t="n">
-        <v>21000</v>
+        <v>129000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터주 급등에 따른 국내 양자컴퓨터 테마 기대감. AI 반도체, 보안 테마 연관성 언급.</t>
+          <t>미국 증시 및 반도체주 급등에 따른 200만 돌파 기대. 공급 부족 장기화 전망 및 AI 두뇌 역할 강조.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', 'AI반도체']</t>
+          <t>['반도체', 'AI', '공급 부족']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1314,13 +1314,13 @@
         <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>748</v>
+        <v>796</v>
       </c>
       <c r="F10" t="n">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="G10" t="n">
-        <v>3060</v>
+        <v>3129</v>
       </c>
       <c r="H10" t="n">
         <v>46.48</v>
@@ -1346,7 +1346,7 @@
         <v>46.52</v>
       </c>
       <c r="O10" t="n">
-        <v>605444648000</v>
+        <v>693269293000</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1355,10 +1355,10 @@
         <v>78600</v>
       </c>
       <c r="R10" t="n">
-        <v>-413000</v>
+        <v>-509000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>226000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>85850</v>
+        <v>17710</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.53%</t>
+          <t>'+2.67%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.04</v>
+        <v>0.27</v>
       </c>
       <c r="E11" t="n">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="F11" t="n">
+        <v>34</v>
+      </c>
+      <c r="G11" t="n">
         <v>78</v>
       </c>
-      <c r="G11" t="n">
-        <v>717</v>
-      </c>
       <c r="H11" t="n">
-        <v>23.23</v>
+        <v>0.97</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>85400</v>
+        <v>17250</v>
       </c>
       <c r="K11" t="n">
-        <v>87300</v>
+        <v>17920</v>
       </c>
       <c r="L11" t="n">
-        <v>87800</v>
+        <v>18440</v>
       </c>
       <c r="M11" t="n">
-        <v>85300</v>
+        <v>17450</v>
       </c>
       <c r="N11" t="n">
-        <v>23.27</v>
+        <v>0.7</v>
       </c>
       <c r="O11" t="n">
-        <v>49877104000</v>
+        <v>58575894750</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>30550</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>6100</v>
       </c>
       <c r="R11" t="n">
-        <v>-54000</v>
+        <v>-82000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 원전주 급등과 대미 투자 관련 발표 가능성 뉴스를 기반으로 주가 상승 기대감이 형성됨. 120일선 돌파 및 장기적 50만원 목표 제시.</t>
+          <t>미국 양자컴퓨터주 급등에 따른 기대감. AI, 양자, 보안 테마 언급. 2만냥 터치 가능성 제시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전주', '대미 투자', '120일선']</t>
+          <t>['양자컴퓨터', 'AI', '보안']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,97 +1476,189 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4280</v>
+        <v>85800</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-7.66%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.4</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="F12" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G12" t="n">
-        <v>494</v>
+        <v>731</v>
       </c>
       <c r="H12" t="n">
-        <v>0.55</v>
+        <v>23.23</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4635</v>
+        <v>85400</v>
       </c>
       <c r="K12" t="n">
-        <v>4465</v>
+        <v>87300</v>
       </c>
       <c r="L12" t="n">
-        <v>4535</v>
+        <v>87800</v>
       </c>
       <c r="M12" t="n">
-        <v>4225</v>
+        <v>85300</v>
       </c>
       <c r="N12" t="n">
-        <v>0.95</v>
+        <v>23.27</v>
       </c>
       <c r="O12" t="n">
-        <v>18645199636</v>
+        <v>53251186550</v>
       </c>
       <c r="P12" t="n">
-        <v>6900</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>1738</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>86000</v>
+        <v>-105000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>STO 사업 추진 및 미국 코인 주식 거래 허용 호재 언급. 스테이블코인 테마 관련 기대감.</t>
+          <t>미국 원전주 급등과 대미 투자 관련 발표 가능성 뉴스를 기반으로 주가 상승 기대감이 형성됨. 120일선 돌파 및 장기적 50만원 목표 제시.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['원전주', '대미 투자', '120일선']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>미투온</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4265</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-7.98%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>110</v>
+      </c>
+      <c r="F13" t="n">
+        <v>70</v>
+      </c>
+      <c r="G13" t="n">
+        <v>515</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>4635</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4465</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4535</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4215</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O13" t="n">
+        <v>20367364018</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6900</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1738</v>
+      </c>
+      <c r="R13" t="n">
+        <v>60000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>STO 사업 추진 및 미국 코인 주식 거래 허용 호재 언급. 스테이블코인 테마 관련 기대감.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
         <v>0.3</v>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>['STO', '스테이블코인']</t>
         </is>
       </c>
-      <c r="X12" t="n">
+      <c r="X13" t="n">
         <v>3</v>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>201490</t>
         </is>
